--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260810.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>17.14%</t>
+          <t>16.94%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3,450,000</t>
+          <t>79,000,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.45%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>79,000,000</t>
+          <t>3,450,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.35%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.61%</t>
+          <t>4.71%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,495,000</t>
+          <t>1,550,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.60%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>4.26%</t>
         </is>
       </c>
     </row>
@@ -770,117 +770,117 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.67%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>3,040,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,040,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,030,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>7,500,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>877,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -909,44 +909,44 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>199,500</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>184,500</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -968,161 +968,161 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>5,200,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>2,646,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,646,000</t>
+          <t>1,750,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,750,000</t>
+          <t>897,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>897,000</t>
+          <t>3,700,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1161,78 +1161,78 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,330,000</t>
+          <t>5,360,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>260,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>260,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1298,51 +1298,51 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1415,39 +1415,39 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1496,46 +1496,46 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,39 +1547,39 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>336,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>13,948,211,949</t>
+          <t>10,774,005,494</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-434,637,689</t>
+          <t>723,888,865</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
